--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-16T10:47:22.228Z</t>
+    <t>2026-06-16T12:50:53.613Z</t>
   </si>
   <si>
     <t>Stagwell | Transforming Marketing</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-16T10:47:22.228Z</t>
+    <t>2026-06-17T04:20:42.664Z</t>
   </si>
   <si>
     <t>Stagwell | Transforming Marketing</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-17T04:20:42.664Z</t>
+    <t>2026-06-17T07:07:10.094Z</t>
   </si>
   <si>
     <t>Stagwell | Transforming Marketing</t>
